--- a/output/pdf_financials_xlsx/WI.xlsx
+++ b/output/pdf_financials_xlsx/WI.xlsx
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.03494</v>
+        <v>-0.03494</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-1.583829</v>
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.03494</v>
+        <v>-0.03494</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-1.583829</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.03494</v>
+        <v>-0.03494</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-1.583829</v>
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-1.747</v>
+        <v>1.747</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>9.716742</v>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.03494</v>
+        <v>-0.03494</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-1.583829</v>
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.03494</v>
+        <v>-0.03494</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-1.583829</v>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -30866,10 +30866,10 @@
         </is>
       </c>
       <c r="E388" s="5" t="n">
-        <v>0.03494</v>
+        <v>-0.03494</v>
       </c>
       <c r="F388" s="5" t="n">
-        <v>1.583829</v>
+        <v>-1.583829</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         </is>
       </c>
       <c r="E391" s="5" t="n">
-        <v>0.03494</v>
+        <v>-0.03494</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/WI.xlsx
+++ b/output/pdf_financials_xlsx/WI.xlsx
@@ -843,13 +843,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.046932</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002455</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002896</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0.06604500000000001</v>
@@ -1444,13 +1444,13 @@
         <v>-1.583829</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.434397</v>
+        <v>-0.481329</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.131531</v>
+        <v>1.129076</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.252643</v>
+        <v>1.249747</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.773289</v>
@@ -1518,13 +1518,13 @@
         <v>-1.583829</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.434397</v>
+        <v>-0.481329</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.131531</v>
+        <v>1.129076</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.252643</v>
+        <v>1.249747</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.773289</v>
@@ -1716,16 +1716,16 @@
         <v>2.1303</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.008182999999999999</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.149868</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.023318</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.025715</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.618673</v>
@@ -1790,16 +1790,16 @@
         <v>2.1303</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.008182999999999999</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.149868</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.023318</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.025715</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.618673</v>
@@ -2234,16 +2234,16 @@
         <v>8.634493000000001</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.135021</v>
+        <v>0.126838</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.175517</v>
+        <v>0.025649</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.05134</v>
+        <v>0.028022</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.415915</v>
+        <v>0.3902</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -23648,7 +23648,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -25436,7 +25436,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -28638,7 +28638,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">

--- a/output/pdf_financials_xlsx/WI.xlsx
+++ b/output/pdf_financials_xlsx/WI.xlsx
@@ -670,10 +670,10 @@
         <v>0.229643</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.386463</v>
+        <v>0.402303</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.400123</v>
+        <v>1.525032</v>
       </c>
     </row>
     <row r="8">
@@ -781,10 +781,10 @@
         <v>0.271446</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.482187</v>
+        <v>0.498027</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.845133</v>
+        <v>1.970042</v>
       </c>
     </row>
     <row r="11">
@@ -4432,13 +4432,13 @@
         <v>-0.352779</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>0.551547</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>1.949619</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>7.738307</v>
       </c>
     </row>
     <row r="107">
@@ -4972,22 +4972,22 @@
         <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.14088</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-0.006764</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-0.045908</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-0.036199</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-0.019045</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-0.029726</v>
       </c>
       <c r="J121" s="3" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>0</v>
+        <v>-0.0165</v>
       </c>
       <c r="I128" s="3" t="n">
         <v>0</v>
@@ -14424,7 +14424,11 @@
           <t>Deferred tax recovery 20</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -14552,7 +14556,11 @@
           <t>Net change in non-cash balances related to operations 24</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -16764,7 +16772,11 @@
           <t>Deferred tax recovery (note 20)</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -16892,7 +16904,11 @@
           <t>Net change in non-cash balances related to operations (note 24)</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -17748,7 +17764,11 @@
           <t>Share repurchase</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -19110,7 +19130,11 @@
           <t>Financing fees paid</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -19242,7 +19266,11 @@
           <t>Repurchase of shares (note 10)</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -20406,7 +20434,11 @@
           <t>Repurchase of shares (note 8)</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -21590,7 +21622,11 @@
           <t>Repurchase of shares</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -23316,7 +23352,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
